--- a/数值知识库-网页版GPT/源表/D-Item-道具表.xlsx
+++ b/数值知识库-网页版GPT/源表/D-Item-道具表.xlsx
@@ -15639,7 +15639,7 @@
         <v>1</v>
       </c>
       <c r="L158" s="71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M158" s="1" t="s">
         <v>53</v>
@@ -15698,7 +15698,7 @@
         <v>1</v>
       </c>
       <c r="L159" s="71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M159" s="1" t="s">
         <v>53</v>
@@ -15757,7 +15757,7 @@
         <v>1</v>
       </c>
       <c r="L160" s="71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M160" s="1" t="s">
         <v>53</v>
@@ -15816,7 +15816,7 @@
         <v>1</v>
       </c>
       <c r="L161" s="71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M161" s="1" t="s">
         <v>53</v>
@@ -15875,7 +15875,7 @@
         <v>1</v>
       </c>
       <c r="L162" s="71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M162" s="1" t="s">
         <v>53</v>
@@ -15934,7 +15934,7 @@
         <v>1</v>
       </c>
       <c r="L163" s="71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M163" s="1" t="s">
         <v>53</v>
@@ -15993,7 +15993,7 @@
         <v>1</v>
       </c>
       <c r="L164" s="71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M164" s="1" t="s">
         <v>53</v>
@@ -16052,7 +16052,7 @@
         <v>1</v>
       </c>
       <c r="L165" s="71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M165" s="1" t="s">
         <v>53</v>
@@ -16111,7 +16111,7 @@
         <v>1</v>
       </c>
       <c r="L166" s="71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M166" s="1" t="s">
         <v>53</v>
@@ -16170,7 +16170,7 @@
         <v>1</v>
       </c>
       <c r="L167" s="71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M167" s="1" t="s">
         <v>53</v>
@@ -16229,7 +16229,7 @@
         <v>1</v>
       </c>
       <c r="L168" s="71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M168" s="1" t="s">
         <v>53</v>
@@ -16288,7 +16288,7 @@
         <v>1</v>
       </c>
       <c r="L169" s="71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M169" s="1" t="s">
         <v>53</v>
@@ -16347,7 +16347,7 @@
         <v>1</v>
       </c>
       <c r="L170" s="71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M170" s="1" t="s">
         <v>53</v>
@@ -16406,7 +16406,7 @@
         <v>1</v>
       </c>
       <c r="L171" s="71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M171" s="1" t="s">
         <v>53</v>
@@ -16465,7 +16465,7 @@
         <v>0</v>
       </c>
       <c r="L172" s="71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M172" s="1" t="s">
         <v>53</v>
@@ -16524,7 +16524,7 @@
         <v>1</v>
       </c>
       <c r="L173" s="71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M173" s="1" t="s">
         <v>53</v>
@@ -16583,7 +16583,7 @@
         <v>1</v>
       </c>
       <c r="L174" s="71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M174" s="1" t="s">
         <v>53</v>
@@ -16642,7 +16642,7 @@
         <v>0</v>
       </c>
       <c r="L175" s="71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M175" s="1" t="s">
         <v>53</v>
@@ -16701,7 +16701,7 @@
         <v>0</v>
       </c>
       <c r="L176" s="71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M176" s="1" t="s">
         <v>53</v>
@@ -16760,7 +16760,7 @@
         <v>0</v>
       </c>
       <c r="L177" s="71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M177" s="1" t="s">
         <v>53</v>
@@ -16819,7 +16819,7 @@
         <v>1</v>
       </c>
       <c r="L178" s="71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M178" s="1" t="s">
         <v>53</v>
@@ -16878,7 +16878,7 @@
         <v>0</v>
       </c>
       <c r="L179" s="71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M179" s="1" t="s">
         <v>53</v>
@@ -16937,7 +16937,7 @@
         <v>1</v>
       </c>
       <c r="L180" s="71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M180" s="1" t="s">
         <v>53</v>
@@ -16996,7 +16996,7 @@
         <v>1</v>
       </c>
       <c r="L181" s="71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M181" s="1" t="s">
         <v>53</v>
@@ -17055,7 +17055,7 @@
         <v>1</v>
       </c>
       <c r="L182" s="71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M182" s="1" t="s">
         <v>53</v>
@@ -17114,7 +17114,7 @@
         <v>1</v>
       </c>
       <c r="L183" s="71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M183" s="1" t="s">
         <v>53</v>
@@ -17173,7 +17173,7 @@
         <v>1</v>
       </c>
       <c r="L184" s="71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M184" s="1" t="s">
         <v>53</v>
@@ -17232,7 +17232,7 @@
         <v>0</v>
       </c>
       <c r="L185" s="71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M185" s="1" t="s">
         <v>53</v>
@@ -17293,7 +17293,7 @@
         <v>0</v>
       </c>
       <c r="L186" s="71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M186" s="1" t="s">
         <v>53</v>
@@ -17354,7 +17354,7 @@
         <v>0</v>
       </c>
       <c r="L187" s="71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M187" s="1" t="s">
         <v>53</v>
@@ -17415,7 +17415,7 @@
         <v>1</v>
       </c>
       <c r="L188" s="71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M188" s="1" t="s">
         <v>53</v>
@@ -17476,7 +17476,7 @@
         <v>1</v>
       </c>
       <c r="L189" s="71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M189" s="1" t="s">
         <v>53</v>
@@ -17537,7 +17537,7 @@
         <v>0</v>
       </c>
       <c r="L190" s="71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M190" s="1" t="s">
         <v>53</v>
@@ -17598,7 +17598,7 @@
         <v>0</v>
       </c>
       <c r="L191" s="71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M191" s="1" t="s">
         <v>53</v>
@@ -17659,7 +17659,7 @@
         <v>1</v>
       </c>
       <c r="L192" s="71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M192" s="1" t="s">
         <v>53</v>
@@ -17721,7 +17721,7 @@
         <v>1</v>
       </c>
       <c r="L193" s="71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M193" s="1" t="s">
         <v>978</v>
@@ -17782,7 +17782,7 @@
         <v>1</v>
       </c>
       <c r="L194" s="71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M194" s="1" t="s">
         <v>978</v>
@@ -17843,7 +17843,7 @@
         <v>1</v>
       </c>
       <c r="L195" s="71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M195" s="1" t="s">
         <v>978</v>
@@ -17904,7 +17904,7 @@
         <v>1</v>
       </c>
       <c r="L196" s="71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M196" s="1" t="s">
         <v>978</v>
@@ -17965,7 +17965,7 @@
         <v>1</v>
       </c>
       <c r="L197" s="71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M197" s="1" t="s">
         <v>978</v>
@@ -18079,7 +18079,7 @@
         <v>1</v>
       </c>
       <c r="L200" s="71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M200" s="1" t="s">
         <v>53</v>
@@ -18138,7 +18138,7 @@
         <v>1</v>
       </c>
       <c r="L201" s="71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M201" s="1" t="s">
         <v>53</v>
@@ -18197,7 +18197,7 @@
         <v>1</v>
       </c>
       <c r="L202" s="71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M202" s="1" t="s">
         <v>53</v>
@@ -18256,7 +18256,7 @@
         <v>1</v>
       </c>
       <c r="L203" s="71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M203" s="1" t="s">
         <v>53</v>
@@ -18315,7 +18315,7 @@
         <v>1</v>
       </c>
       <c r="L204" s="71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M204" s="1" t="s">
         <v>53</v>
@@ -18374,7 +18374,7 @@
         <v>1</v>
       </c>
       <c r="L205" s="71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M205" s="1" t="s">
         <v>53</v>
@@ -18433,7 +18433,7 @@
         <v>1</v>
       </c>
       <c r="L206" s="71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M206" s="1" t="s">
         <v>53</v>
@@ -18492,7 +18492,7 @@
         <v>1</v>
       </c>
       <c r="L207" s="71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M207" s="1" t="s">
         <v>53</v>
@@ -18551,7 +18551,7 @@
         <v>1</v>
       </c>
       <c r="L208" s="71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M208" s="1" t="s">
         <v>53</v>
@@ -18610,7 +18610,7 @@
         <v>0</v>
       </c>
       <c r="L209" s="71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M209" s="1" t="s">
         <v>53</v>
@@ -18669,7 +18669,7 @@
         <v>1</v>
       </c>
       <c r="L210" s="71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M210" s="1" t="s">
         <v>53</v>
@@ -18728,7 +18728,7 @@
         <v>1</v>
       </c>
       <c r="L211" s="71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M211" s="1" t="s">
         <v>53</v>
@@ -18787,7 +18787,7 @@
         <v>0</v>
       </c>
       <c r="L212" s="71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M212" s="1" t="s">
         <v>53</v>
@@ -18848,7 +18848,7 @@
         <v>1</v>
       </c>
       <c r="L213" s="71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M213" s="1" t="s">
         <v>53</v>
@@ -18909,7 +18909,7 @@
         <v>1</v>
       </c>
       <c r="L214" s="71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M214" s="1" t="s">
         <v>53</v>
@@ -18970,7 +18970,7 @@
         <v>1</v>
       </c>
       <c r="L215" s="71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M215" s="1" t="s">
         <v>53</v>
@@ -19031,7 +19031,7 @@
         <v>0</v>
       </c>
       <c r="L216" s="71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M216" s="1" t="s">
         <v>53</v>
@@ -19092,7 +19092,7 @@
         <v>1</v>
       </c>
       <c r="L217" s="71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M217" s="1" t="s">
         <v>53</v>
@@ -19154,7 +19154,7 @@
         <v>1</v>
       </c>
       <c r="L218" s="71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M218" s="1" t="s">
         <v>978</v>
@@ -19235,7 +19235,7 @@
         <v>1</v>
       </c>
       <c r="L220" s="71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M220" s="1" t="s">
         <v>53</v>
@@ -19294,7 +19294,7 @@
         <v>1</v>
       </c>
       <c r="L221" s="71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M221" s="1" t="s">
         <v>53</v>
@@ -19353,7 +19353,7 @@
         <v>1</v>
       </c>
       <c r="L222" s="71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M222" s="1" t="s">
         <v>53</v>
@@ -19412,7 +19412,7 @@
         <v>1</v>
       </c>
       <c r="L223" s="71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M223" s="1" t="s">
         <v>53</v>
@@ -19471,7 +19471,7 @@
         <v>1</v>
       </c>
       <c r="L224" s="71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M224" s="1" t="s">
         <v>53</v>
@@ -19530,7 +19530,7 @@
         <v>1</v>
       </c>
       <c r="L225" s="71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M225" s="1" t="s">
         <v>53</v>
@@ -19589,7 +19589,7 @@
         <v>1</v>
       </c>
       <c r="L226" s="71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M226" s="1" t="s">
         <v>53</v>
@@ -19648,7 +19648,7 @@
         <v>1</v>
       </c>
       <c r="L227" s="71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M227" s="1" t="s">
         <v>53</v>
@@ -19707,7 +19707,7 @@
         <v>1</v>
       </c>
       <c r="L228" s="71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M228" s="1" t="s">
         <v>53</v>
@@ -19766,7 +19766,7 @@
         <v>1</v>
       </c>
       <c r="L229" s="71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M229" s="1" t="s">
         <v>53</v>
@@ -19825,7 +19825,7 @@
         <v>1</v>
       </c>
       <c r="L230" s="71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M230" s="1" t="s">
         <v>53</v>
@@ -19884,7 +19884,7 @@
         <v>1</v>
       </c>
       <c r="L231" s="71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M231" s="1" t="s">
         <v>53</v>
@@ -19943,7 +19943,7 @@
         <v>0</v>
       </c>
       <c r="L232" s="71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M232" s="1" t="s">
         <v>53</v>
@@ -20004,7 +20004,7 @@
         <v>1</v>
       </c>
       <c r="L233" s="71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M233" s="1" t="s">
         <v>53</v>
@@ -20063,7 +20063,7 @@
         <v>0</v>
       </c>
       <c r="L234" s="71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M234" s="1" t="s">
         <v>53</v>
@@ -20125,7 +20125,7 @@
         <v>1</v>
       </c>
       <c r="L235" s="71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M235" s="1" t="s">
         <v>978</v>
